--- a/READING/1_21_07.xlsx
+++ b/READING/1_21_07.xlsx
@@ -465,164 +465,168 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>途端に</t>
+          <t>あっという間に</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>とたんに</t>
+          <t>あっというまに</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>正当……时候，刚一……时候</t>
+          <t>一转眼，刹那之间。形容时间过得飞快。</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>あっという間に</t>
+          <t>とんでもない</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>あっというまに</t>
+          <t>とんでもない</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>一转眼，刹那之间。形容时间过得飞快。</t>
+          <t>1. 出乎意料的，惊人的。2. (表示强烈否定) 哪里的话，毫无道理。3. (用于回应感谢或道歉) 别客气，没什么。</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>見積もる</t>
+          <t>途方もない</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>みつもる</t>
+          <t>とほうもない</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>估算；估计；估价；预测</t>
+          <t>惊人的，没谱的，出乎意料的，异想天开的。</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>とんでもない</t>
+          <t>何しろ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>とんでもない</t>
+          <t>なにしろ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1. 出乎意料的，惊人的。2. (表示强烈否定) 哪里的话，毫无道理。3. (用于回应感谢或道歉) 别客气，没什么。</t>
+          <t>总之，毕竟，因为。用于在开头引出理由或情况。</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>しっかり</t>
+          <t>見積もる</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>しっかり</t>
+          <t>みつもる</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>牢固地，可靠地，扎实地。</t>
+          <t>估算；估计；估价；预测</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>～にしたら</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>もてあます</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>もてあます</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>从…立场来看</t>
+          <t>(因过大、过强或过剩而) 不知如何处理，难以对付。</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>途方もない</t>
+          <t>途端に</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>とほうもない</t>
+          <t>とたんに</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>惊人的，没谱的，出乎意料的，异想天开的。</t>
+          <t>正当……时候，刚一……时候</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>苦手</t>
+          <t>しっかり</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>にがて</t>
+          <t>しっかり</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>不擅长，不善于应付。</t>
+          <t>牢固地，可靠地，扎实地。</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -633,17 +637,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>何しろ</t>
+          <t>～なので</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>なにしろ</t>
+          <t>～なので</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>总之，毕竟，因为。用于在开头引出理由或情况。</t>
+          <t>因为...，所以...。</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -654,17 +658,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>～に依ると</t>
+          <t>苦手</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>～によると</t>
+          <t>にがて</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>根据...，据...。</t>
+          <t>不擅长，不善于应付。</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -675,17 +679,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>～なので</t>
+          <t>～に依ると</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>～なので</t>
+          <t>～によると</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>因为...，所以...。</t>
+          <t>根据...，据...。</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -696,17 +700,13 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>もてあます</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>もてあます</t>
-        </is>
-      </c>
+          <t>～にしたら</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>(因过大、过强或过剩而) 不知如何处理，难以对付。</t>
+          <t>从…立场来看</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -738,17 +738,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>持ち運び</t>
+          <t>経験</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>もちはこび</t>
+          <t>けいけん</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>携带，搬运。</t>
+          <t>经验，经历，体验。</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -759,20 +759,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ご/お～する/します/いたす</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>ようがない</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ようがない</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>自谦</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>ご/お～です-&gt;尊他</t>
-        </is>
-      </c>
+          <t>无法...，没法…</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -780,17 +780,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>無断</t>
+          <t>きちんと</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>むだん</t>
+          <t>きちんと</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>擅自；未经允许</t>
+          <t>整齐地，规矩地，好好地。</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -801,17 +801,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>とる</t>
+          <t>無理に</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>とる</t>
+          <t>むりに</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>拿，取。选择</t>
+          <t>强制地。</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -839,17 +839,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>きちんと</t>
+          <t>持ち運び</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>きちんと</t>
+          <t>もちはこび</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>整齐地，规矩地，好好地。</t>
+          <t>携带，搬运。</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -860,17 +860,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ようがない</t>
+          <t>とる</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ようがない</t>
+          <t>とる</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>无法...，没法…</t>
+          <t>拿，取。选择</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -881,17 +881,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>経験</t>
+          <t>無断</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>けいけん</t>
+          <t>むだん</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>经验，经历，体验。</t>
+          <t>擅自；未经允许</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -902,20 +902,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>無理に</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>むりに</t>
-        </is>
-      </c>
+          <t>ご/お～する/します/いたす</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>强制地。</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
+          <t>自谦</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>ご/お～です-&gt;尊他</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -923,17 +923,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>とれる</t>
+          <t>～者です</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>とれる</t>
+          <t>～ものです</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1. 脱落，掉下。2. 可以解释为，可以理解为。3. 消除，去除(疲劳、疼痛等)。</t>
+          <t>(自谦表达) 我是做...的人。</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -944,17 +944,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>そのもの</t>
+          <t>辺り</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>そのもの</t>
+          <t>あたり</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>...本身，就是那个。用于加强语气，强调事物自身。</t>
+          <t>大约；附近；周围；</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -965,17 +965,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>～とおり</t>
+          <t>反応なく</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>～とおり</t>
+          <t>はんのうなく</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>如同...，按照...。</t>
+          <t>没有反应，毫无反应地。</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -986,20 +986,16 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>まだ</t>
+          <t>ご/お～いただく</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>还…</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>だだ-&gt;只不过</t>
-        </is>
-      </c>
+          <t>承蒙您…</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1007,17 +1003,13 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>それだけ</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>それだけ</t>
-        </is>
-      </c>
+          <t>または</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1. 只有那些，仅此而已。2. 正因为如此，到那种程度。</t>
+          <t>或者。</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -1028,17 +1020,13 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>取れる</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>とれる</t>
-        </is>
-      </c>
+          <t>～ようだ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>去除；脱落；理解</t>
+          <t>好像；看样子；似乎</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -1049,17 +1037,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>あえて</t>
+          <t>まずい</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>あえて</t>
+          <t>まずい</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>硬是，敢于，特意。表示明知困难或不必如此，却偏要去做。</t>
+          <t>难吃的; 糟糕的，不妙的。</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -1070,17 +1058,13 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>思い出</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>おもいで</t>
-        </is>
-      </c>
+          <t>～たがる</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>回忆；追忆</t>
+          <t>(第三人称) 想要...。</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -1091,17 +1075,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>すぐに</t>
+          <t>保護者</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>すぐに</t>
+          <t>ほごしゃ</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>马上，立刻。</t>
+          <t>监护人（如父母）</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -1112,24 +1096,20 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>～たら</t>
+          <t>立ち寄る</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>～たら</t>
+          <t>たちよる</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>如果...的话；（确定条件）...之后就...。</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>なら-&gt;如果</t>
-        </is>
-      </c>
+          <t>顺便去，顺路到...。</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1137,17 +1117,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>それどころか</t>
+          <t>注文</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>それどころか</t>
+          <t>ちゅうもん</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>岂止如此，不仅如此，反而...。用于引出与前述事实更进一步或相反的情况。</t>
+          <t>点菜，订购，要求。</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1158,17 +1138,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>かつて</t>
+          <t>なくす</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>かつて</t>
+          <t>なくす</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>曾经，以往。</t>
+          <t>弄丢，消除。</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -1179,20 +1159,20 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ご/お～です</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>～ばかり</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>～ばかり</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>尊他</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>ご/お～する/します/いたす-&gt;自谦</t>
-        </is>
-      </c>
+          <t>净是，光是...</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1200,17 +1180,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>なくす</t>
+          <t>かつて</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>なくす</t>
+          <t>かつて</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>弄丢，消除。</t>
+          <t>曾经，以往。</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -1221,20 +1201,20 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>～ばかり</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>～ばかり</t>
-        </is>
-      </c>
+          <t>ご/お～です</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>净是，光是...</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
+          <t>尊他</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>ご/お～する/します/いたす-&gt;自谦</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1242,17 +1222,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>～者です</t>
+          <t>とれる</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>～ものです</t>
+          <t>とれる</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>(自谦表达) 我是做...的人。</t>
+          <t>1. 脱落，掉下。2. 可以解释为，可以理解为。3. 消除，去除(疲劳、疼痛等)。</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -1263,17 +1243,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>立ち寄る</t>
+          <t>そのもの</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>たちよる</t>
+          <t>そのもの</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>顺便去，顺路到...。</t>
+          <t>...本身，就是那个。用于加强语气，强调事物自身。</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -1284,20 +1264,20 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>まずい</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>まずい</t>
-        </is>
-      </c>
+          <t>まだ</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>难吃的; 糟糕的，不妙的。</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
+          <t>还…</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>だだ-&gt;只不过</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1305,17 +1285,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>保護者</t>
+          <t>取れる</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ほごしゃ</t>
+          <t>とれる</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>监护人（如父母）</t>
+          <t>去除；脱落；理解</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -1326,17 +1306,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>注文</t>
+          <t>あえて</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ちゅうもん</t>
+          <t>あえて</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>点菜，订购，要求。</t>
+          <t>硬是，敢于，特意。表示明知困难或不必如此，却偏要去做。</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -1347,17 +1327,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>辺り</t>
+          <t>それだけ</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>あたり</t>
+          <t>それだけ</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>大约；附近；周围；</t>
+          <t>1. 只有那些，仅此而已。2. 正因为如此，到那种程度。</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -1368,13 +1348,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>～ようだ</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>すぐに</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>すぐに</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>好像；看样子；似乎</t>
+          <t>马上，立刻。</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -1385,16 +1369,24 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>～たがる</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>～たら</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>～たら</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>(第三人称) 想要...。</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
+          <t>如果...的话；（确定条件）...之后就...。</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>なら-&gt;如果</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1402,13 +1394,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>または</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>それどころか</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>それどころか</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>或者。</t>
+          <t>岂止如此，不仅如此，反而...。用于引出与前述事实更进一步或相反的情况。</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -1419,13 +1415,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ご/お～いただく</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>思い出</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>おもいで</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>承蒙您…</t>
+          <t>回忆；追忆</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -1436,17 +1436,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>反応なく</t>
+          <t>～とおり</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>はんのうなく</t>
+          <t>～とおり</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>没有反应，毫无反应地。</t>
+          <t>如同...，按照...。</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>

--- a/READING/1_21_07.xlsx
+++ b/READING/1_21_07.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\READING\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A4EDD6B-C192-41F3-ABE7-F9BAC51552BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58FD0021-8961-43FE-A10C-7577D067919D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14820" yWindow="4275" windowWidth="23580" windowHeight="9255" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16320" yWindow="885" windowWidth="27840" windowHeight="20040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="282">
   <si>
     <t>Fre</t>
   </si>
@@ -400,13 +400,679 @@
   </si>
   <si>
     <t>积累；装载；堆积</t>
+  </si>
+  <si>
+    <t>...てから</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在…之后</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>片付く</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>かたづく</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>整理好；收拾整齐；解决；处理好</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ております</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)处于…状态(2)正在…</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>同"ている"</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>間に合う</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>赶得上；来得及</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>進める</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>すすめる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>推进；促进；进行</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>私の場合</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>对于我来说…</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>おそらく</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>恐怕</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>みたいに</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>～たとたん（に）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚一…就…</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>像…一样</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>急に</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>突然；忽然</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>頭が固い</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>あたまがかたい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>思想顽固</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ような</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>像…那样</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ふつう</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>常见，平常</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>けれども</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>但是</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ないといけない</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>没有…是不行的</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>要するに</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ようするに</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>总之；简而言之</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>アドバイス</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>advice</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>次第で</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>根据…</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>意欲</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>干劲</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>授業</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>课堂，教学</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>かける</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>主动向对方发起的动作</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>好きに</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>自由地；尽情地</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>異なる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不同;不一样</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>決まり</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>规定；规矩；决定</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>何か</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>某事；某物</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>つくる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>制作；创造</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>つける</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"-&gt;附着;添加"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>かける</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"-&gt;花费</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>見つけ出す</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(主动)发掘</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>仕方</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>方法；办法；做法</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ではないか</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)难道不是…吗(2)是否…</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>すれ違い</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>擦肩而过</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>近づく</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ちかづく</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>靠近；接近</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>すれちがい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>甘やかされる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>被溺爱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>遭遇</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>そうぐう</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>遇到</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>"である"-&gt;"です"</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>シグナル</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>信号；标志</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>なんなのか</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>到底是什么</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>あるなし</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否…</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>にしたがった</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>遵从，遵守</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>たほうがよい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>最好…</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>または</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>或者</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>“あるいは”-&gt;或者；有时</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>にもとづいて</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>基于；以...为基础</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>けが</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>受伤；负伤</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>身につける</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>学会；掌握</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>いやいや</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不情愿的</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>本格的</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>正式的</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>私達</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>我们</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>わたしたち</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>とんでもない</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)非常地…(2)惊人地(3)岂有此理；哪里的话</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>もったいない</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>浪费</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ぐらい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)到了…地步(程度)(2)大约</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>どんどん</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>逐渐；越来越</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>退屈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>たいくつ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>无聊；厌倦</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>そんなに</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>那样地</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>途方もない</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>无法想象;极其困难</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ますます</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>越来越</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>否応なく</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>强制地。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>割り込む</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>わりこむ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>插入；打断；插队；插话</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>じゅうぶん</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>足够；充分</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>耐えられる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>能够忍受</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>だけの</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>足以…的</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ぜんぶ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>全部</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>切る</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)完全(2)切断</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>すくなく</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>至少</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>あわただしい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>匆忙的</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>済ませる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>果たす</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成；实现；履行</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>はがき</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>明信片</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>問い合わせ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>咨询；询问</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>明記</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>明确记载；清楚写明</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>どちらか</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>哪一个；哪一方；哪个</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>開催日</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>かいさいび</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>举行日; 举办日</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>いたします</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>"します"谦让语</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -426,6 +1092,29 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="2">
@@ -463,11 +1152,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -770,13 +1464,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E120"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="26.375" customWidth="1"/>
     <col min="3" max="3" width="19.5" customWidth="1"/>
     <col min="4" max="4" width="29.125" customWidth="1"/>
+    <col min="5" max="5" width="45.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.15">
@@ -1439,7 +2134,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A49">
         <v>0</v>
       </c>
@@ -1453,7 +2148,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A50">
         <v>0</v>
       </c>
@@ -1465,6 +2160,824 @@
       </c>
       <c r="D50" t="s">
         <v>125</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A51">
+        <v>2</v>
+      </c>
+      <c r="B51" t="s">
+        <v>126</v>
+      </c>
+      <c r="D51" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A52">
+        <v>2</v>
+      </c>
+      <c r="B52" t="s">
+        <v>128</v>
+      </c>
+      <c r="C52" t="s">
+        <v>129</v>
+      </c>
+      <c r="D52" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A53">
+        <v>2</v>
+      </c>
+      <c r="B53" t="s">
+        <v>131</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D53" t="s">
+        <v>132</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A54">
+        <v>2</v>
+      </c>
+      <c r="B54" t="s">
+        <v>134</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A55">
+        <v>2</v>
+      </c>
+      <c r="B55" t="s">
+        <v>136</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D55" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A56">
+        <v>2</v>
+      </c>
+      <c r="B56" t="s">
+        <v>139</v>
+      </c>
+      <c r="D56" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A57">
+        <v>2</v>
+      </c>
+      <c r="B57" t="s">
+        <v>141</v>
+      </c>
+      <c r="D57" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A58">
+        <v>2</v>
+      </c>
+      <c r="B58" t="s">
+        <v>143</v>
+      </c>
+      <c r="D58" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A59">
+        <v>2</v>
+      </c>
+      <c r="B59" t="s">
+        <v>144</v>
+      </c>
+      <c r="D59" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A60">
+        <v>2</v>
+      </c>
+      <c r="B60" t="s">
+        <v>147</v>
+      </c>
+      <c r="D60" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A61">
+        <v>2</v>
+      </c>
+      <c r="B61" t="s">
+        <v>149</v>
+      </c>
+      <c r="C61" t="s">
+        <v>150</v>
+      </c>
+      <c r="D61" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A62">
+        <v>2</v>
+      </c>
+      <c r="B62" t="s">
+        <v>152</v>
+      </c>
+      <c r="D62" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A63">
+        <v>2</v>
+      </c>
+      <c r="B63" t="s">
+        <v>154</v>
+      </c>
+      <c r="C63" t="s">
+        <v>155</v>
+      </c>
+      <c r="D63" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A64">
+        <v>2</v>
+      </c>
+      <c r="B64" t="s">
+        <v>157</v>
+      </c>
+      <c r="D64" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A65">
+        <v>2</v>
+      </c>
+      <c r="B65" t="s">
+        <v>159</v>
+      </c>
+      <c r="D65" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A66">
+        <v>2</v>
+      </c>
+      <c r="B66" t="s">
+        <v>161</v>
+      </c>
+      <c r="C66" t="s">
+        <v>162</v>
+      </c>
+      <c r="D66" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A67">
+        <v>2</v>
+      </c>
+      <c r="B67" t="s">
+        <v>164</v>
+      </c>
+      <c r="D67" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A68">
+        <v>2</v>
+      </c>
+      <c r="B68" t="s">
+        <v>166</v>
+      </c>
+      <c r="D68" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A69">
+        <v>2</v>
+      </c>
+      <c r="B69" t="s">
+        <v>168</v>
+      </c>
+      <c r="D69" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A70">
+        <v>2</v>
+      </c>
+      <c r="B70" t="s">
+        <v>170</v>
+      </c>
+      <c r="D70" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A71">
+        <v>2</v>
+      </c>
+      <c r="B71" t="s">
+        <v>172</v>
+      </c>
+      <c r="D71" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A72">
+        <v>2</v>
+      </c>
+      <c r="B72" t="s">
+        <v>174</v>
+      </c>
+      <c r="D72" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A73">
+        <v>2</v>
+      </c>
+      <c r="B73" t="s">
+        <v>176</v>
+      </c>
+      <c r="D73" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A74">
+        <v>2</v>
+      </c>
+      <c r="B74" t="s">
+        <v>178</v>
+      </c>
+      <c r="D74" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A75">
+        <v>2</v>
+      </c>
+      <c r="B75" t="s">
+        <v>180</v>
+      </c>
+      <c r="D75" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A76">
+        <v>2</v>
+      </c>
+      <c r="B76" t="s">
+        <v>182</v>
+      </c>
+      <c r="D76" t="s">
+        <v>183</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A77">
+        <v>2</v>
+      </c>
+      <c r="B77" t="s">
+        <v>185</v>
+      </c>
+      <c r="D77" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A78">
+        <v>2</v>
+      </c>
+      <c r="B78" t="s">
+        <v>187</v>
+      </c>
+      <c r="D78" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A79">
+        <v>2</v>
+      </c>
+      <c r="B79" t="s">
+        <v>189</v>
+      </c>
+      <c r="D79" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A80">
+        <v>2</v>
+      </c>
+      <c r="B80" t="s">
+        <v>191</v>
+      </c>
+      <c r="C80" t="s">
+        <v>196</v>
+      </c>
+      <c r="D80" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A81">
+        <v>2</v>
+      </c>
+      <c r="B81" t="s">
+        <v>193</v>
+      </c>
+      <c r="C81" t="s">
+        <v>194</v>
+      </c>
+      <c r="D81" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A82">
+        <v>2</v>
+      </c>
+      <c r="B82" t="s">
+        <v>197</v>
+      </c>
+      <c r="D82" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A83">
+        <v>2</v>
+      </c>
+      <c r="B83" t="s">
+        <v>199</v>
+      </c>
+      <c r="C83" t="s">
+        <v>200</v>
+      </c>
+      <c r="D83" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A84">
+        <v>2</v>
+      </c>
+      <c r="B84" t="s">
+        <v>203</v>
+      </c>
+      <c r="D84" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A85">
+        <v>2</v>
+      </c>
+      <c r="B85" t="s">
+        <v>205</v>
+      </c>
+      <c r="D85" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A86">
+        <v>2</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="D86" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A87">
+        <v>2</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="D87" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A88">
+        <v>2</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="D88" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A89">
+        <v>2</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="D89" t="s">
+        <v>214</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A90">
+        <v>2</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="D90" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A91">
+        <v>2</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="D91" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A92">
+        <v>2</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="D92" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A93">
+        <v>2</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="D93" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A94">
+        <v>2</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="D94" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A95">
+        <v>2</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C95" t="s">
+        <v>228</v>
+      </c>
+      <c r="D95" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A96">
+        <v>2</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="D96" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A97">
+        <v>2</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="D97" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A98">
+        <v>2</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="D98" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A99">
+        <v>2</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="D99" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A100">
+        <v>2</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C100" t="s">
+        <v>238</v>
+      </c>
+      <c r="D100" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A101">
+        <v>2</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="D101" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A102">
+        <v>2</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D102" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A103">
+        <v>2</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D103" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A104">
+        <v>2</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D104" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A105">
+        <v>2</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="C105" t="s">
+        <v>249</v>
+      </c>
+      <c r="D105" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A106">
+        <v>2</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="D106" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A107">
+        <v>2</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="D107" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A108">
+        <v>2</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="D108" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A109">
+        <v>2</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="D109" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A110">
+        <v>2</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="D110" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A111">
+        <v>2</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="D111" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A112">
+        <v>2</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="D112" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A113">
+        <v>2</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="D113" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A114">
+        <v>2</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="D114" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A115">
+        <v>2</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D115" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A116">
+        <v>2</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="D116" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A117">
+        <v>2</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="D117" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A118">
+        <v>2</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="D118" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A119">
+        <v>2</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="C119" t="s">
+        <v>278</v>
+      </c>
+      <c r="D119" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A120">
+        <v>2</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="D120" t="s">
+        <v>281</v>
       </c>
     </row>
   </sheetData>

--- a/READING/1_21_07.xlsx
+++ b/READING/1_21_07.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E120"/>
+  <dimension ref="A1:F120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -463,6 +463,11 @@
           <t>备注</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -480,6 +485,11 @@
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,6 +507,11 @@
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -514,6 +529,11 @@
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -535,6 +555,11 @@
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -552,10 +577,15 @@
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -573,6 +603,11 @@
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -590,6 +625,11 @@
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -611,10 +651,15 @@
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -628,10 +673,15 @@
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -645,6 +695,11 @@
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -666,6 +721,11 @@
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -683,6 +743,11 @@
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -704,10 +769,15 @@
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -721,10 +791,15 @@
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -738,6 +813,11 @@
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -759,6 +839,11 @@
           <t>"つける"-&gt;附着;添加"かける"-&gt;花费</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -776,6 +861,11 @@
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -793,10 +883,15 @@
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -814,6 +909,11 @@
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -831,6 +931,11 @@
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -848,6 +953,11 @@
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -873,6 +983,11 @@
           <t>"である"-&gt;"です"</t>
         </is>
       </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -894,6 +1009,11 @@
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -915,6 +1035,11 @@
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -932,10 +1057,15 @@
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -949,6 +1079,11 @@
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -970,10 +1105,15 @@
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -987,6 +1127,11 @@
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1008,6 +1153,11 @@
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1025,6 +1175,11 @@
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1046,6 +1201,11 @@
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1067,6 +1227,11 @@
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1084,6 +1249,11 @@
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1101,10 +1271,15 @@
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1122,6 +1297,11 @@
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1139,6 +1319,11 @@
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1156,6 +1341,11 @@
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1173,6 +1363,11 @@
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1194,6 +1389,11 @@
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1211,6 +1411,11 @@
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1228,6 +1433,11 @@
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1245,6 +1455,11 @@
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1266,6 +1481,11 @@
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1287,6 +1507,11 @@
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1308,6 +1533,11 @@
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1325,6 +1555,11 @@
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1342,6 +1577,11 @@
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1359,6 +1599,11 @@
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1376,6 +1621,11 @@
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1393,6 +1643,11 @@
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1410,6 +1665,11 @@
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1427,6 +1687,11 @@
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1444,6 +1709,11 @@
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1461,6 +1731,11 @@
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1478,6 +1753,11 @@
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1495,6 +1775,11 @@
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1512,6 +1797,11 @@
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1529,6 +1819,11 @@
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1546,6 +1841,11 @@
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1563,6 +1863,11 @@
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1580,6 +1885,11 @@
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1601,6 +1911,11 @@
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1618,6 +1933,11 @@
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1635,10 +1955,15 @@
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -1652,6 +1977,11 @@
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1673,6 +2003,11 @@
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1694,10 +2029,15 @@
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -1715,10 +2055,15 @@
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -1736,6 +2081,11 @@
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1753,6 +2103,11 @@
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -1770,6 +2125,11 @@
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -1791,6 +2151,11 @@
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -1812,10 +2177,15 @@
           <t>“あるいは”-&gt;或者；有时</t>
         </is>
       </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -1829,6 +2199,11 @@
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -1850,6 +2225,11 @@
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -1867,6 +2247,11 @@
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -1884,6 +2269,11 @@
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -1901,6 +2291,11 @@
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -1918,6 +2313,11 @@
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -1935,6 +2335,11 @@
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -1952,6 +2357,11 @@
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -1969,6 +2379,11 @@
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -1986,6 +2401,11 @@
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -2003,6 +2423,11 @@
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -2024,6 +2449,11 @@
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -2045,6 +2475,11 @@
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -2066,6 +2501,11 @@
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -2087,6 +2527,11 @@
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -2108,6 +2553,11 @@
           <t>ご/お～です-&gt;尊他</t>
         </is>
       </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -2129,6 +2579,11 @@
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -2150,6 +2605,11 @@
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -2171,6 +2631,11 @@
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -2192,10 +2657,15 @@
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -2213,6 +2683,11 @@
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -2234,6 +2709,11 @@
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -2255,6 +2735,11 @@
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -2276,6 +2761,11 @@
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -2297,6 +2787,11 @@
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -2318,6 +2813,11 @@
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -2343,6 +2843,11 @@
           <t>なら-&gt;如果</t>
         </is>
       </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -2364,6 +2869,11 @@
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -2385,6 +2895,11 @@
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -2406,6 +2921,11 @@
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -2427,6 +2947,11 @@
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -2448,6 +2973,11 @@
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -2465,6 +2995,11 @@
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -2486,6 +3021,11 @@
           <t>だだ-&gt;只不过</t>
         </is>
       </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -2507,6 +3047,11 @@
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -2524,6 +3069,11 @@
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -2545,6 +3095,11 @@
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -2562,6 +3117,11 @@
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -2583,6 +3143,11 @@
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -2604,6 +3169,11 @@
           <t>ご/お～する/します/いたす-&gt;自谦</t>
         </is>
       </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -2625,6 +3195,11 @@
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -2646,6 +3221,11 @@
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -2667,6 +3247,11 @@
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -2688,10 +3273,15 @@
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -2705,6 +3295,11 @@
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -2726,6 +3321,11 @@
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/READING/1_21_07.xlsx
+++ b/READING/1_21_07.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\READING\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDEE530F-49BC-4095-A58C-53EE5756E5C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC642E25-4974-41AF-BA0A-DD88F8B22F7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17520" yWindow="1005" windowWidth="20880" windowHeight="19995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19215" yWindow="1005" windowWidth="19185" windowHeight="19995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,9 +24,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="284">
   <si>
-    <t>Fre</t>
-  </si>
-  <si>
     <t>单词</t>
   </si>
   <si>
@@ -876,13 +873,17 @@
   </si>
   <si>
     <t>2</t>
+  </si>
+  <si>
+    <t>Fre</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -902,6 +903,13 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -939,9 +947,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1257,23 +1268,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
       <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.15">
@@ -1281,13 +1292,13 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
       <c r="F2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.15">
@@ -1295,13 +1306,13 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
       <c r="F3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.15">
@@ -1309,13 +1320,13 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
         <v>11</v>
       </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
       <c r="F4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.15">
@@ -1323,16 +1334,16 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>14</v>
       </c>
-      <c r="D5" t="s">
-        <v>15</v>
-      </c>
       <c r="F5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.15">
@@ -1340,13 +1351,13 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
         <v>16</v>
       </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
       <c r="F6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.15">
@@ -1354,16 +1365,16 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
         <v>18</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>19</v>
       </c>
-      <c r="D7" t="s">
+      <c r="F7" t="s">
         <v>20</v>
-      </c>
-      <c r="F7" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.15">
@@ -1371,13 +1382,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" t="s">
         <v>22</v>
       </c>
-      <c r="D8" t="s">
-        <v>23</v>
-      </c>
       <c r="F8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.15">
@@ -1385,16 +1396,16 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" t="s">
         <v>24</v>
       </c>
-      <c r="C9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" t="s">
-        <v>25</v>
-      </c>
       <c r="F9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.15">
@@ -1402,13 +1413,13 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" t="s">
         <v>26</v>
       </c>
-      <c r="D10" t="s">
-        <v>27</v>
-      </c>
       <c r="F10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.15">
@@ -1416,13 +1427,13 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" t="s">
         <v>28</v>
       </c>
-      <c r="D11" t="s">
-        <v>29</v>
-      </c>
       <c r="F11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.15">
@@ -1430,16 +1441,16 @@
         <v>5</v>
       </c>
       <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" t="s">
         <v>30</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>31</v>
       </c>
-      <c r="D12" t="s">
-        <v>32</v>
-      </c>
       <c r="F12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.15">
@@ -1447,13 +1458,13 @@
         <v>5</v>
       </c>
       <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" t="s">
         <v>33</v>
       </c>
-      <c r="D13" t="s">
-        <v>34</v>
-      </c>
       <c r="F13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.15">
@@ -1461,16 +1472,16 @@
         <v>4</v>
       </c>
       <c r="B14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" t="s">
         <v>35</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>36</v>
       </c>
-      <c r="D14" t="s">
-        <v>37</v>
-      </c>
       <c r="F14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.15">
@@ -1478,13 +1489,13 @@
         <v>5</v>
       </c>
       <c r="B15" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" t="s">
         <v>38</v>
       </c>
-      <c r="D15" t="s">
-        <v>39</v>
-      </c>
       <c r="F15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.15">
@@ -1492,13 +1503,13 @@
         <v>5</v>
       </c>
       <c r="B16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" t="s">
         <v>40</v>
       </c>
-      <c r="D16" t="s">
-        <v>41</v>
-      </c>
       <c r="F16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.15">
@@ -1506,16 +1517,16 @@
         <v>4</v>
       </c>
       <c r="B17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" t="s">
         <v>42</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>43</v>
       </c>
-      <c r="E17" t="s">
-        <v>44</v>
-      </c>
       <c r="F17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.15">
@@ -1523,13 +1534,13 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" t="s">
         <v>45</v>
       </c>
-      <c r="D18" t="s">
-        <v>46</v>
-      </c>
       <c r="F18" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.15">
@@ -1537,13 +1548,13 @@
         <v>4</v>
       </c>
       <c r="B19" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" t="s">
         <v>47</v>
       </c>
-      <c r="D19" t="s">
-        <v>48</v>
-      </c>
       <c r="F19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.15">
@@ -1551,16 +1562,16 @@
         <v>6</v>
       </c>
       <c r="B20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" t="s">
         <v>49</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>50</v>
       </c>
-      <c r="D20" t="s">
-        <v>51</v>
-      </c>
       <c r="F20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.15">
@@ -1568,13 +1579,13 @@
         <v>4</v>
       </c>
       <c r="B21" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" t="s">
         <v>52</v>
       </c>
-      <c r="D21" t="s">
-        <v>53</v>
-      </c>
       <c r="F21" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.15">
@@ -1582,13 +1593,13 @@
         <v>4</v>
       </c>
       <c r="B22" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" t="s">
         <v>54</v>
       </c>
-      <c r="D22" t="s">
-        <v>55</v>
-      </c>
       <c r="F22" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.15">
@@ -1596,19 +1607,19 @@
         <v>4</v>
       </c>
       <c r="B23" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" t="s">
         <v>56</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>57</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>58</v>
       </c>
-      <c r="E23" t="s">
-        <v>59</v>
-      </c>
       <c r="F23" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.15">
@@ -1616,16 +1627,16 @@
         <v>4</v>
       </c>
       <c r="B24" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" t="s">
         <v>60</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>61</v>
       </c>
-      <c r="D24" t="s">
-        <v>62</v>
-      </c>
       <c r="F24" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.15">
@@ -1633,16 +1644,16 @@
         <v>3</v>
       </c>
       <c r="B25" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" t="s">
+        <v>62</v>
+      </c>
+      <c r="D25" t="s">
         <v>63</v>
       </c>
-      <c r="C25" t="s">
-        <v>63</v>
-      </c>
-      <c r="D25" t="s">
-        <v>64</v>
-      </c>
       <c r="F25" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.15">
@@ -1650,13 +1661,13 @@
         <v>3</v>
       </c>
       <c r="B26" t="s">
+        <v>64</v>
+      </c>
+      <c r="D26" t="s">
         <v>65</v>
       </c>
-      <c r="D26" t="s">
-        <v>66</v>
-      </c>
       <c r="F26" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.15">
@@ -1664,13 +1675,13 @@
         <v>4</v>
       </c>
       <c r="B27" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" t="s">
         <v>67</v>
       </c>
-      <c r="D27" t="s">
-        <v>68</v>
-      </c>
       <c r="F27" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.15">
@@ -1678,16 +1689,16 @@
         <v>3</v>
       </c>
       <c r="B28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C28" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" t="s">
         <v>69</v>
       </c>
-      <c r="C28" t="s">
-        <v>69</v>
-      </c>
-      <c r="D28" t="s">
-        <v>70</v>
-      </c>
       <c r="F28" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.15">
@@ -1695,13 +1706,13 @@
         <v>4</v>
       </c>
       <c r="B29" t="s">
+        <v>70</v>
+      </c>
+      <c r="D29" t="s">
         <v>71</v>
       </c>
-      <c r="D29" t="s">
-        <v>72</v>
-      </c>
       <c r="F29" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.15">
@@ -1709,16 +1720,16 @@
         <v>3</v>
       </c>
       <c r="B30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C30" t="s">
+        <v>72</v>
+      </c>
+      <c r="D30" t="s">
         <v>73</v>
       </c>
-      <c r="C30" t="s">
-        <v>73</v>
-      </c>
-      <c r="D30" t="s">
-        <v>74</v>
-      </c>
       <c r="F30" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.15">
@@ -1726,13 +1737,13 @@
         <v>3</v>
       </c>
       <c r="B31" t="s">
+        <v>74</v>
+      </c>
+      <c r="D31" t="s">
         <v>75</v>
       </c>
-      <c r="D31" t="s">
-        <v>76</v>
-      </c>
       <c r="F31" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.15">
@@ -1740,16 +1751,16 @@
         <v>3</v>
       </c>
       <c r="B32" t="s">
+        <v>76</v>
+      </c>
+      <c r="C32" t="s">
         <v>77</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>78</v>
       </c>
-      <c r="D32" t="s">
-        <v>79</v>
-      </c>
       <c r="F32" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.15">
@@ -1757,16 +1768,16 @@
         <v>3</v>
       </c>
       <c r="B33" t="s">
+        <v>79</v>
+      </c>
+      <c r="C33" t="s">
+        <v>79</v>
+      </c>
+      <c r="D33" t="s">
         <v>80</v>
       </c>
-      <c r="C33" t="s">
-        <v>80</v>
-      </c>
-      <c r="D33" t="s">
-        <v>81</v>
-      </c>
       <c r="F33" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.15">
@@ -1774,13 +1785,13 @@
         <v>3</v>
       </c>
       <c r="B34" t="s">
+        <v>81</v>
+      </c>
+      <c r="D34" t="s">
         <v>82</v>
       </c>
-      <c r="D34" t="s">
-        <v>83</v>
-      </c>
       <c r="F34" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.15">
@@ -1788,13 +1799,13 @@
         <v>3</v>
       </c>
       <c r="B35" t="s">
+        <v>83</v>
+      </c>
+      <c r="D35" t="s">
         <v>84</v>
       </c>
-      <c r="D35" t="s">
-        <v>85</v>
-      </c>
       <c r="F35" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.15">
@@ -1802,16 +1813,16 @@
         <v>4</v>
       </c>
       <c r="B36" t="s">
+        <v>85</v>
+      </c>
+      <c r="C36" t="s">
         <v>86</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
         <v>87</v>
       </c>
-      <c r="D36" t="s">
-        <v>88</v>
-      </c>
       <c r="F36" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.15">
@@ -1819,13 +1830,13 @@
         <v>3</v>
       </c>
       <c r="B37" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D37" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F37" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.15">
@@ -1833,13 +1844,13 @@
         <v>3</v>
       </c>
       <c r="B38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D38" t="s">
         <v>90</v>
       </c>
-      <c r="D38" t="s">
-        <v>91</v>
-      </c>
       <c r="F38" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.15">
@@ -1847,13 +1858,13 @@
         <v>3</v>
       </c>
       <c r="B39" t="s">
+        <v>91</v>
+      </c>
+      <c r="D39" t="s">
         <v>92</v>
       </c>
-      <c r="D39" t="s">
-        <v>93</v>
-      </c>
       <c r="F39" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.15">
@@ -1861,16 +1872,16 @@
         <v>3</v>
       </c>
       <c r="B40" t="s">
+        <v>93</v>
+      </c>
+      <c r="C40" t="s">
         <v>94</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
         <v>95</v>
       </c>
-      <c r="D40" t="s">
-        <v>96</v>
-      </c>
       <c r="F40" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.15">
@@ -1878,13 +1889,13 @@
         <v>2</v>
       </c>
       <c r="B41" t="s">
+        <v>96</v>
+      </c>
+      <c r="D41" t="s">
         <v>97</v>
       </c>
-      <c r="D41" t="s">
-        <v>98</v>
-      </c>
       <c r="F41" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.15">
@@ -1892,13 +1903,13 @@
         <v>2</v>
       </c>
       <c r="B42" t="s">
+        <v>98</v>
+      </c>
+      <c r="D42" t="s">
         <v>99</v>
       </c>
-      <c r="D42" t="s">
-        <v>100</v>
-      </c>
       <c r="F42" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.15">
@@ -1906,13 +1917,13 @@
         <v>2</v>
       </c>
       <c r="B43" t="s">
+        <v>100</v>
+      </c>
+      <c r="D43" t="s">
         <v>101</v>
       </c>
-      <c r="D43" t="s">
-        <v>102</v>
-      </c>
       <c r="F43" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.15">
@@ -1920,16 +1931,16 @@
         <v>2</v>
       </c>
       <c r="B44" t="s">
+        <v>102</v>
+      </c>
+      <c r="C44" t="s">
         <v>103</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
         <v>104</v>
       </c>
-      <c r="D44" t="s">
-        <v>105</v>
-      </c>
       <c r="F44" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.15">
@@ -1937,16 +1948,16 @@
         <v>2</v>
       </c>
       <c r="B45" t="s">
+        <v>105</v>
+      </c>
+      <c r="C45" t="s">
         <v>106</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D45" t="s">
         <v>107</v>
       </c>
-      <c r="D45" t="s">
-        <v>108</v>
-      </c>
       <c r="F45" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.15">
@@ -1954,16 +1965,16 @@
         <v>2</v>
       </c>
       <c r="B46" t="s">
+        <v>108</v>
+      </c>
+      <c r="C46" t="s">
         <v>109</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>110</v>
       </c>
-      <c r="D46" t="s">
-        <v>111</v>
-      </c>
       <c r="F46" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.15">
@@ -1971,13 +1982,13 @@
         <v>2</v>
       </c>
       <c r="B47" t="s">
+        <v>111</v>
+      </c>
+      <c r="D47" t="s">
         <v>112</v>
       </c>
-      <c r="D47" t="s">
-        <v>113</v>
-      </c>
       <c r="F47" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.15">
@@ -1985,13 +1996,13 @@
         <v>2</v>
       </c>
       <c r="B48" t="s">
+        <v>113</v>
+      </c>
+      <c r="D48" t="s">
         <v>114</v>
       </c>
-      <c r="D48" t="s">
-        <v>115</v>
-      </c>
       <c r="F48" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.15">
@@ -1999,13 +2010,13 @@
         <v>2</v>
       </c>
       <c r="B49" t="s">
+        <v>115</v>
+      </c>
+      <c r="D49" t="s">
         <v>116</v>
       </c>
-      <c r="D49" t="s">
-        <v>117</v>
-      </c>
       <c r="F49" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.15">
@@ -2013,13 +2024,13 @@
         <v>2</v>
       </c>
       <c r="B50" t="s">
+        <v>117</v>
+      </c>
+      <c r="D50" t="s">
         <v>118</v>
       </c>
-      <c r="D50" t="s">
-        <v>119</v>
-      </c>
       <c r="F50" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.15">
@@ -2027,13 +2038,13 @@
         <v>2</v>
       </c>
       <c r="B51" t="s">
+        <v>119</v>
+      </c>
+      <c r="D51" t="s">
         <v>120</v>
       </c>
-      <c r="D51" t="s">
-        <v>121</v>
-      </c>
       <c r="F51" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.15">
@@ -2041,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B52" t="s">
+        <v>121</v>
+      </c>
+      <c r="D52" t="s">
         <v>122</v>
       </c>
-      <c r="D52" t="s">
-        <v>123</v>
-      </c>
       <c r="F52" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.15">
@@ -2055,13 +2066,13 @@
         <v>2</v>
       </c>
       <c r="B53" t="s">
+        <v>123</v>
+      </c>
+      <c r="D53" t="s">
         <v>124</v>
       </c>
-      <c r="D53" t="s">
-        <v>125</v>
-      </c>
       <c r="F53" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.15">
@@ -2069,13 +2080,13 @@
         <v>2</v>
       </c>
       <c r="B54" t="s">
+        <v>125</v>
+      </c>
+      <c r="D54" t="s">
         <v>126</v>
       </c>
-      <c r="D54" t="s">
-        <v>127</v>
-      </c>
       <c r="F54" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.15">
@@ -2083,13 +2094,13 @@
         <v>2</v>
       </c>
       <c r="B55" t="s">
+        <v>127</v>
+      </c>
+      <c r="D55" t="s">
         <v>128</v>
       </c>
-      <c r="D55" t="s">
-        <v>129</v>
-      </c>
       <c r="F55" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.15">
@@ -2097,13 +2108,13 @@
         <v>2</v>
       </c>
       <c r="B56" t="s">
+        <v>129</v>
+      </c>
+      <c r="D56" t="s">
         <v>130</v>
       </c>
-      <c r="D56" t="s">
-        <v>131</v>
-      </c>
       <c r="F56" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.15">
@@ -2111,13 +2122,13 @@
         <v>2</v>
       </c>
       <c r="B57" t="s">
+        <v>131</v>
+      </c>
+      <c r="D57" t="s">
         <v>132</v>
       </c>
-      <c r="D57" t="s">
-        <v>133</v>
-      </c>
       <c r="F57" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.15">
@@ -2125,13 +2136,13 @@
         <v>2</v>
       </c>
       <c r="B58" t="s">
+        <v>133</v>
+      </c>
+      <c r="D58" t="s">
         <v>134</v>
       </c>
-      <c r="D58" t="s">
-        <v>135</v>
-      </c>
       <c r="F58" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.15">
@@ -2139,13 +2150,13 @@
         <v>2</v>
       </c>
       <c r="B59" t="s">
+        <v>135</v>
+      </c>
+      <c r="D59" t="s">
         <v>136</v>
       </c>
-      <c r="D59" t="s">
-        <v>137</v>
-      </c>
       <c r="F59" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.15">
@@ -2153,13 +2164,13 @@
         <v>2</v>
       </c>
       <c r="B60" t="s">
+        <v>137</v>
+      </c>
+      <c r="D60" t="s">
         <v>138</v>
       </c>
-      <c r="D60" t="s">
-        <v>139</v>
-      </c>
       <c r="F60" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.15">
@@ -2167,13 +2178,13 @@
         <v>2</v>
       </c>
       <c r="B61" t="s">
+        <v>139</v>
+      </c>
+      <c r="D61" t="s">
         <v>140</v>
       </c>
-      <c r="D61" t="s">
-        <v>141</v>
-      </c>
       <c r="F61" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.15">
@@ -2181,13 +2192,13 @@
         <v>2</v>
       </c>
       <c r="B62" t="s">
+        <v>141</v>
+      </c>
+      <c r="D62" t="s">
         <v>142</v>
       </c>
-      <c r="D62" t="s">
-        <v>143</v>
-      </c>
       <c r="F62" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.15">
@@ -2195,16 +2206,16 @@
         <v>2</v>
       </c>
       <c r="B63" t="s">
+        <v>143</v>
+      </c>
+      <c r="C63" t="s">
         <v>144</v>
       </c>
-      <c r="C63" t="s">
+      <c r="D63" t="s">
         <v>145</v>
       </c>
-      <c r="D63" t="s">
-        <v>146</v>
-      </c>
       <c r="F63" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.15">
@@ -2212,13 +2223,13 @@
         <v>2</v>
       </c>
       <c r="B64" t="s">
+        <v>146</v>
+      </c>
+      <c r="D64" t="s">
         <v>147</v>
       </c>
-      <c r="D64" t="s">
-        <v>148</v>
-      </c>
       <c r="F64" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.15">
@@ -2226,13 +2237,13 @@
         <v>2</v>
       </c>
       <c r="B65" t="s">
+        <v>148</v>
+      </c>
+      <c r="D65" t="s">
         <v>149</v>
       </c>
-      <c r="D65" t="s">
-        <v>150</v>
-      </c>
       <c r="F65" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.15">
@@ -2240,13 +2251,13 @@
         <v>3</v>
       </c>
       <c r="B66" t="s">
+        <v>150</v>
+      </c>
+      <c r="D66" t="s">
         <v>151</v>
       </c>
-      <c r="D66" t="s">
-        <v>152</v>
-      </c>
       <c r="F66" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.15">
@@ -2254,16 +2265,16 @@
         <v>2</v>
       </c>
       <c r="B67" t="s">
+        <v>152</v>
+      </c>
+      <c r="C67" t="s">
         <v>153</v>
       </c>
-      <c r="C67" t="s">
+      <c r="D67" t="s">
         <v>154</v>
       </c>
-      <c r="D67" t="s">
-        <v>155</v>
-      </c>
       <c r="F67" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.15">
@@ -2271,16 +2282,16 @@
         <v>2</v>
       </c>
       <c r="B68" t="s">
+        <v>155</v>
+      </c>
+      <c r="C68" t="s">
         <v>156</v>
       </c>
-      <c r="C68" t="s">
+      <c r="D68" t="s">
         <v>157</v>
       </c>
-      <c r="D68" t="s">
-        <v>158</v>
-      </c>
       <c r="F68" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.15">
@@ -2288,16 +2299,16 @@
         <v>3</v>
       </c>
       <c r="B69" t="s">
+        <v>158</v>
+      </c>
+      <c r="C69" t="s">
         <v>159</v>
       </c>
-      <c r="C69" t="s">
+      <c r="D69" t="s">
         <v>160</v>
       </c>
-      <c r="D69" t="s">
-        <v>161</v>
-      </c>
       <c r="F69" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.15">
@@ -2305,16 +2316,16 @@
         <v>3</v>
       </c>
       <c r="B70" t="s">
+        <v>161</v>
+      </c>
+      <c r="C70" t="s">
         <v>162</v>
       </c>
-      <c r="C70" t="s">
+      <c r="D70" t="s">
         <v>163</v>
       </c>
-      <c r="D70" t="s">
-        <v>164</v>
-      </c>
       <c r="F70" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.15">
@@ -2322,13 +2333,13 @@
         <v>2</v>
       </c>
       <c r="B71" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D71" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F71" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.15">
@@ -2336,13 +2347,13 @@
         <v>2</v>
       </c>
       <c r="B72" t="s">
+        <v>165</v>
+      </c>
+      <c r="D72" t="s">
         <v>166</v>
       </c>
-      <c r="D72" t="s">
-        <v>167</v>
-      </c>
       <c r="F72" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.15">
@@ -2350,16 +2361,16 @@
         <v>2</v>
       </c>
       <c r="B73" t="s">
+        <v>167</v>
+      </c>
+      <c r="C73" t="s">
         <v>168</v>
       </c>
-      <c r="C73" t="s">
+      <c r="D73" t="s">
         <v>169</v>
       </c>
-      <c r="D73" t="s">
-        <v>170</v>
-      </c>
       <c r="F73" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.15">
@@ -2367,16 +2378,16 @@
         <v>2</v>
       </c>
       <c r="B74" t="s">
+        <v>170</v>
+      </c>
+      <c r="D74" t="s">
         <v>171</v>
       </c>
-      <c r="D74" t="s">
+      <c r="E74" t="s">
         <v>172</v>
       </c>
-      <c r="E74" t="s">
-        <v>173</v>
-      </c>
       <c r="F74" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.15">
@@ -2384,13 +2395,13 @@
         <v>3</v>
       </c>
       <c r="B75" t="s">
+        <v>173</v>
+      </c>
+      <c r="D75" t="s">
         <v>174</v>
       </c>
-      <c r="D75" t="s">
-        <v>175</v>
-      </c>
       <c r="F75" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.15">
@@ -2398,16 +2409,16 @@
         <v>2</v>
       </c>
       <c r="B76" t="s">
+        <v>175</v>
+      </c>
+      <c r="C76" t="s">
         <v>176</v>
       </c>
-      <c r="C76" t="s">
+      <c r="D76" t="s">
         <v>177</v>
       </c>
-      <c r="D76" t="s">
-        <v>178</v>
-      </c>
       <c r="F76" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.15">
@@ -2415,13 +2426,13 @@
         <v>2</v>
       </c>
       <c r="B77" t="s">
+        <v>178</v>
+      </c>
+      <c r="D77" t="s">
         <v>179</v>
       </c>
-      <c r="D77" t="s">
-        <v>180</v>
-      </c>
       <c r="F77" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.15">
@@ -2429,13 +2440,13 @@
         <v>2</v>
       </c>
       <c r="B78" t="s">
+        <v>180</v>
+      </c>
+      <c r="D78" t="s">
         <v>181</v>
       </c>
-      <c r="D78" t="s">
-        <v>182</v>
-      </c>
       <c r="F78" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.15">
@@ -2443,13 +2454,13 @@
         <v>2</v>
       </c>
       <c r="B79" t="s">
+        <v>182</v>
+      </c>
+      <c r="D79" t="s">
         <v>183</v>
       </c>
-      <c r="D79" t="s">
-        <v>184</v>
-      </c>
       <c r="F79" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.15">
@@ -2457,13 +2468,13 @@
         <v>2</v>
       </c>
       <c r="B80" t="s">
+        <v>184</v>
+      </c>
+      <c r="D80" t="s">
         <v>185</v>
       </c>
-      <c r="D80" t="s">
-        <v>186</v>
-      </c>
       <c r="F80" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.15">
@@ -2471,13 +2482,13 @@
         <v>2</v>
       </c>
       <c r="B81" t="s">
+        <v>186</v>
+      </c>
+      <c r="D81" t="s">
         <v>187</v>
       </c>
-      <c r="D81" t="s">
-        <v>188</v>
-      </c>
       <c r="F81" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.15">
@@ -2485,13 +2496,13 @@
         <v>2</v>
       </c>
       <c r="B82" t="s">
+        <v>188</v>
+      </c>
+      <c r="D82" t="s">
         <v>189</v>
       </c>
-      <c r="D82" t="s">
-        <v>190</v>
-      </c>
       <c r="F82" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.15">
@@ -2499,13 +2510,13 @@
         <v>2</v>
       </c>
       <c r="B83" t="s">
+        <v>190</v>
+      </c>
+      <c r="D83" t="s">
         <v>191</v>
       </c>
-      <c r="D83" t="s">
-        <v>192</v>
-      </c>
       <c r="F83" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.15">
@@ -2513,13 +2524,13 @@
         <v>2</v>
       </c>
       <c r="B84" t="s">
+        <v>192</v>
+      </c>
+      <c r="D84" t="s">
         <v>193</v>
       </c>
-      <c r="D84" t="s">
-        <v>194</v>
-      </c>
       <c r="F84" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.15">
@@ -2527,13 +2538,13 @@
         <v>2</v>
       </c>
       <c r="B85" t="s">
+        <v>194</v>
+      </c>
+      <c r="D85" t="s">
         <v>195</v>
       </c>
-      <c r="D85" t="s">
-        <v>196</v>
-      </c>
       <c r="F85" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.15">
@@ -2541,16 +2552,16 @@
         <v>1</v>
       </c>
       <c r="B86" t="s">
+        <v>196</v>
+      </c>
+      <c r="C86" t="s">
+        <v>196</v>
+      </c>
+      <c r="D86" t="s">
         <v>197</v>
       </c>
-      <c r="C86" t="s">
-        <v>197</v>
-      </c>
-      <c r="D86" t="s">
-        <v>198</v>
-      </c>
       <c r="F86" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.15">
@@ -2558,16 +2569,16 @@
         <v>1</v>
       </c>
       <c r="B87" t="s">
+        <v>198</v>
+      </c>
+      <c r="C87" t="s">
         <v>199</v>
       </c>
-      <c r="C87" t="s">
+      <c r="D87" t="s">
         <v>200</v>
       </c>
-      <c r="D87" t="s">
-        <v>201</v>
-      </c>
       <c r="F87" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.15">
@@ -2575,16 +2586,16 @@
         <v>1</v>
       </c>
       <c r="B88" t="s">
+        <v>201</v>
+      </c>
+      <c r="C88" t="s">
         <v>202</v>
       </c>
-      <c r="C88" t="s">
-        <v>203</v>
-      </c>
       <c r="D88" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F88" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.15">
@@ -2592,16 +2603,16 @@
         <v>1</v>
       </c>
       <c r="B89" t="s">
+        <v>203</v>
+      </c>
+      <c r="C89" t="s">
+        <v>203</v>
+      </c>
+      <c r="D89" t="s">
         <v>204</v>
       </c>
-      <c r="C89" t="s">
-        <v>204</v>
-      </c>
-      <c r="D89" t="s">
-        <v>205</v>
-      </c>
       <c r="F89" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.15">
@@ -2609,16 +2620,16 @@
         <v>1</v>
       </c>
       <c r="B90" t="s">
+        <v>205</v>
+      </c>
+      <c r="D90" t="s">
         <v>206</v>
       </c>
-      <c r="D90" t="s">
+      <c r="E90" t="s">
         <v>207</v>
       </c>
-      <c r="E90" t="s">
-        <v>208</v>
-      </c>
       <c r="F90" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.15">
@@ -2626,16 +2637,16 @@
         <v>1</v>
       </c>
       <c r="B91" t="s">
+        <v>208</v>
+      </c>
+      <c r="C91" t="s">
         <v>209</v>
       </c>
-      <c r="C91" t="s">
+      <c r="D91" t="s">
         <v>210</v>
       </c>
-      <c r="D91" t="s">
-        <v>211</v>
-      </c>
       <c r="F91" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.15">
@@ -2643,16 +2654,16 @@
         <v>1</v>
       </c>
       <c r="B92" t="s">
+        <v>211</v>
+      </c>
+      <c r="C92" t="s">
         <v>212</v>
       </c>
-      <c r="C92" t="s">
+      <c r="D92" t="s">
         <v>213</v>
       </c>
-      <c r="D92" t="s">
-        <v>214</v>
-      </c>
       <c r="F92" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.15">
@@ -2660,16 +2671,16 @@
         <v>1</v>
       </c>
       <c r="B93" t="s">
+        <v>214</v>
+      </c>
+      <c r="C93" t="s">
+        <v>214</v>
+      </c>
+      <c r="D93" t="s">
         <v>215</v>
       </c>
-      <c r="C93" t="s">
-        <v>215</v>
-      </c>
-      <c r="D93" t="s">
-        <v>216</v>
-      </c>
       <c r="F93" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.15">
@@ -2677,16 +2688,16 @@
         <v>0</v>
       </c>
       <c r="B94" t="s">
+        <v>216</v>
+      </c>
+      <c r="C94" t="s">
+        <v>216</v>
+      </c>
+      <c r="D94" t="s">
         <v>217</v>
       </c>
-      <c r="C94" t="s">
-        <v>217</v>
-      </c>
-      <c r="D94" t="s">
-        <v>218</v>
-      </c>
       <c r="F94" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.15">
@@ -2694,16 +2705,16 @@
         <v>1</v>
       </c>
       <c r="B95" t="s">
+        <v>218</v>
+      </c>
+      <c r="C95" t="s">
         <v>219</v>
       </c>
-      <c r="C95" t="s">
+      <c r="D95" t="s">
         <v>220</v>
       </c>
-      <c r="D95" t="s">
-        <v>221</v>
-      </c>
       <c r="F95" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.15">
@@ -2711,16 +2722,16 @@
         <v>0</v>
       </c>
       <c r="B96" t="s">
+        <v>221</v>
+      </c>
+      <c r="C96" t="s">
+        <v>221</v>
+      </c>
+      <c r="D96" t="s">
         <v>222</v>
       </c>
-      <c r="C96" t="s">
-        <v>222</v>
-      </c>
-      <c r="D96" t="s">
-        <v>223</v>
-      </c>
       <c r="F96" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.15">
@@ -2728,16 +2739,16 @@
         <v>0</v>
       </c>
       <c r="B97" t="s">
+        <v>223</v>
+      </c>
+      <c r="C97" t="s">
+        <v>223</v>
+      </c>
+      <c r="D97" t="s">
         <v>224</v>
       </c>
-      <c r="C97" t="s">
-        <v>224</v>
-      </c>
-      <c r="D97" t="s">
-        <v>225</v>
-      </c>
       <c r="F97" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.15">
@@ -2745,16 +2756,16 @@
         <v>0</v>
       </c>
       <c r="B98" t="s">
+        <v>225</v>
+      </c>
+      <c r="C98" t="s">
+        <v>225</v>
+      </c>
+      <c r="D98" t="s">
         <v>226</v>
       </c>
-      <c r="C98" t="s">
-        <v>226</v>
-      </c>
-      <c r="D98" t="s">
-        <v>227</v>
-      </c>
       <c r="F98" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.15">
@@ -2762,16 +2773,16 @@
         <v>0</v>
       </c>
       <c r="B99" t="s">
+        <v>227</v>
+      </c>
+      <c r="C99" t="s">
+        <v>227</v>
+      </c>
+      <c r="D99" t="s">
         <v>228</v>
       </c>
-      <c r="C99" t="s">
-        <v>228</v>
-      </c>
-      <c r="D99" t="s">
-        <v>229</v>
-      </c>
       <c r="F99" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.15">
@@ -2779,16 +2790,16 @@
         <v>0</v>
       </c>
       <c r="B100" t="s">
+        <v>229</v>
+      </c>
+      <c r="C100" t="s">
         <v>230</v>
       </c>
-      <c r="C100" t="s">
+      <c r="D100" t="s">
         <v>231</v>
       </c>
-      <c r="D100" t="s">
-        <v>232</v>
-      </c>
       <c r="F100" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.15">
@@ -2796,19 +2807,19 @@
         <v>0</v>
       </c>
       <c r="B101" t="s">
+        <v>232</v>
+      </c>
+      <c r="C101" t="s">
+        <v>232</v>
+      </c>
+      <c r="D101" t="s">
         <v>233</v>
       </c>
-      <c r="C101" t="s">
-        <v>233</v>
-      </c>
-      <c r="D101" t="s">
+      <c r="E101" t="s">
         <v>234</v>
       </c>
-      <c r="E101" t="s">
-        <v>235</v>
-      </c>
       <c r="F101" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.15">
@@ -2816,16 +2827,16 @@
         <v>0</v>
       </c>
       <c r="B102" t="s">
+        <v>235</v>
+      </c>
+      <c r="C102" t="s">
+        <v>235</v>
+      </c>
+      <c r="D102" t="s">
         <v>236</v>
       </c>
-      <c r="C102" t="s">
-        <v>236</v>
-      </c>
-      <c r="D102" t="s">
-        <v>237</v>
-      </c>
       <c r="F102" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.15">
@@ -2833,16 +2844,16 @@
         <v>0</v>
       </c>
       <c r="B103" t="s">
+        <v>237</v>
+      </c>
+      <c r="C103" t="s">
         <v>238</v>
       </c>
-      <c r="C103" t="s">
+      <c r="D103" t="s">
         <v>239</v>
       </c>
-      <c r="D103" t="s">
-        <v>240</v>
-      </c>
       <c r="F103" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.15">
@@ -2850,16 +2861,16 @@
         <v>0</v>
       </c>
       <c r="B104" t="s">
+        <v>240</v>
+      </c>
+      <c r="C104" t="s">
+        <v>225</v>
+      </c>
+      <c r="D104" t="s">
         <v>241</v>
       </c>
-      <c r="C104" t="s">
-        <v>226</v>
-      </c>
-      <c r="D104" t="s">
-        <v>242</v>
-      </c>
       <c r="F104" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.15">
@@ -2867,16 +2878,16 @@
         <v>0</v>
       </c>
       <c r="B105" t="s">
+        <v>242</v>
+      </c>
+      <c r="C105" t="s">
+        <v>242</v>
+      </c>
+      <c r="D105" t="s">
         <v>243</v>
       </c>
-      <c r="C105" t="s">
-        <v>243</v>
-      </c>
-      <c r="D105" t="s">
-        <v>244</v>
-      </c>
       <c r="F105" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.15">
@@ -2884,16 +2895,16 @@
         <v>0</v>
       </c>
       <c r="B106" t="s">
+        <v>244</v>
+      </c>
+      <c r="C106" t="s">
         <v>245</v>
       </c>
-      <c r="C106" t="s">
+      <c r="D106" t="s">
         <v>246</v>
       </c>
-      <c r="D106" t="s">
-        <v>247</v>
-      </c>
       <c r="F106" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.15">
@@ -2901,13 +2912,13 @@
         <v>0</v>
       </c>
       <c r="B107" t="s">
+        <v>247</v>
+      </c>
+      <c r="D107" t="s">
         <v>248</v>
       </c>
-      <c r="D107" t="s">
-        <v>249</v>
-      </c>
       <c r="F107" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.15">
@@ -2915,16 +2926,16 @@
         <v>0</v>
       </c>
       <c r="B108" t="s">
+        <v>249</v>
+      </c>
+      <c r="D108" t="s">
         <v>250</v>
       </c>
-      <c r="D108" t="s">
+      <c r="E108" t="s">
         <v>251</v>
       </c>
-      <c r="E108" t="s">
-        <v>252</v>
-      </c>
       <c r="F108" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.15">
@@ -2932,16 +2943,16 @@
         <v>0</v>
       </c>
       <c r="B109" t="s">
+        <v>252</v>
+      </c>
+      <c r="C109" t="s">
         <v>253</v>
       </c>
-      <c r="C109" t="s">
+      <c r="D109" t="s">
         <v>254</v>
       </c>
-      <c r="D109" t="s">
-        <v>255</v>
-      </c>
       <c r="F109" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.15">
@@ -2949,13 +2960,13 @@
         <v>0</v>
       </c>
       <c r="B110" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D110" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F110" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.15">
@@ -2963,16 +2974,16 @@
         <v>0</v>
       </c>
       <c r="B111" t="s">
+        <v>256</v>
+      </c>
+      <c r="C111" t="s">
         <v>257</v>
       </c>
-      <c r="C111" t="s">
+      <c r="D111" t="s">
         <v>258</v>
       </c>
-      <c r="D111" t="s">
-        <v>259</v>
-      </c>
       <c r="F111" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.15">
@@ -2980,13 +2991,13 @@
         <v>0</v>
       </c>
       <c r="B112" t="s">
+        <v>259</v>
+      </c>
+      <c r="D112" t="s">
         <v>260</v>
       </c>
-      <c r="D112" t="s">
-        <v>261</v>
-      </c>
       <c r="F112" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.15">
@@ -2994,16 +3005,16 @@
         <v>0</v>
       </c>
       <c r="B113" t="s">
+        <v>261</v>
+      </c>
+      <c r="C113" t="s">
+        <v>261</v>
+      </c>
+      <c r="D113" t="s">
         <v>262</v>
       </c>
-      <c r="C113" t="s">
-        <v>262</v>
-      </c>
-      <c r="D113" t="s">
-        <v>263</v>
-      </c>
       <c r="F113" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.15">
@@ -3011,16 +3022,16 @@
         <v>0</v>
       </c>
       <c r="B114" t="s">
+        <v>263</v>
+      </c>
+      <c r="D114" t="s">
         <v>264</v>
       </c>
-      <c r="D114" t="s">
+      <c r="E114" t="s">
         <v>265</v>
       </c>
-      <c r="E114" t="s">
-        <v>266</v>
-      </c>
       <c r="F114" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.15">
@@ -3028,16 +3039,16 @@
         <v>0</v>
       </c>
       <c r="B115" t="s">
+        <v>266</v>
+      </c>
+      <c r="C115" t="s">
+        <v>266</v>
+      </c>
+      <c r="D115" t="s">
         <v>267</v>
       </c>
-      <c r="C115" t="s">
-        <v>267</v>
-      </c>
-      <c r="D115" t="s">
-        <v>268</v>
-      </c>
       <c r="F115" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.15">
@@ -3045,16 +3056,16 @@
         <v>0</v>
       </c>
       <c r="B116" t="s">
+        <v>268</v>
+      </c>
+      <c r="C116" t="s">
+        <v>268</v>
+      </c>
+      <c r="D116" t="s">
         <v>269</v>
       </c>
-      <c r="C116" t="s">
-        <v>269</v>
-      </c>
-      <c r="D116" t="s">
-        <v>270</v>
-      </c>
       <c r="F116" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.15">
@@ -3062,16 +3073,16 @@
         <v>0</v>
       </c>
       <c r="B117" t="s">
+        <v>270</v>
+      </c>
+      <c r="C117" t="s">
         <v>271</v>
       </c>
-      <c r="C117" t="s">
+      <c r="D117" t="s">
         <v>272</v>
       </c>
-      <c r="D117" t="s">
-        <v>273</v>
-      </c>
       <c r="F117" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.15">
@@ -3079,16 +3090,16 @@
         <v>0</v>
       </c>
       <c r="B118" t="s">
+        <v>273</v>
+      </c>
+      <c r="C118" t="s">
         <v>274</v>
       </c>
-      <c r="C118" t="s">
+      <c r="D118" t="s">
         <v>275</v>
       </c>
-      <c r="D118" t="s">
-        <v>276</v>
-      </c>
       <c r="F118" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.15">
@@ -3096,13 +3107,13 @@
         <v>1</v>
       </c>
       <c r="B119" t="s">
+        <v>276</v>
+      </c>
+      <c r="D119" t="s">
         <v>277</v>
       </c>
-      <c r="D119" t="s">
-        <v>278</v>
-      </c>
       <c r="F119" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.15">
@@ -3110,16 +3121,16 @@
         <v>0</v>
       </c>
       <c r="B120" t="s">
+        <v>278</v>
+      </c>
+      <c r="C120" t="s">
+        <v>278</v>
+      </c>
+      <c r="D120" t="s">
         <v>279</v>
       </c>
-      <c r="C120" t="s">
-        <v>279</v>
-      </c>
-      <c r="D120" t="s">
-        <v>280</v>
-      </c>
       <c r="F120" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.15">
@@ -3127,13 +3138,13 @@
         <v>1</v>
       </c>
       <c r="B121" t="s">
+        <v>280</v>
+      </c>
+      <c r="D121" t="s">
         <v>281</v>
       </c>
-      <c r="D121" t="s">
+      <c r="F121" t="s">
         <v>282</v>
-      </c>
-      <c r="F121" t="s">
-        <v>283</v>
       </c>
     </row>
   </sheetData>

--- a/READING/1_21_07.xlsx
+++ b/READING/1_21_07.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\READING\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC642E25-4974-41AF-BA0A-DD88F8B22F7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34837C36-D02E-441B-B503-431EFF80F494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19215" yWindow="1005" windowWidth="19185" windowHeight="19995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17325" yWindow="1680" windowWidth="22995" windowHeight="19995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="292">
   <si>
     <t>单词</t>
   </si>
@@ -96,9 +96,6 @@
     <t>もてあます</t>
   </si>
   <si>
-    <t>(因过大、过强或过剩而) 不知如何处理，难以对付。</t>
-  </si>
-  <si>
     <t>いやいや</t>
   </si>
   <si>
@@ -153,21 +150,9 @@
     <t>制作；创造</t>
   </si>
   <si>
-    <t>"つける"-&gt;附着;添加"かける"-&gt;花费</t>
-  </si>
-  <si>
-    <t>けが</t>
-  </si>
-  <si>
     <t>受伤；负伤</t>
   </si>
   <si>
-    <t>かける</t>
-  </si>
-  <si>
-    <t>主动向对方发起的动作</t>
-  </si>
-  <si>
     <t>割り込む</t>
   </si>
   <si>
@@ -516,9 +501,6 @@
     <t>惊人的，没谱的，出乎意料的，异想天开的。</t>
   </si>
   <si>
-    <t>无法想象;极其困难</t>
-  </si>
-  <si>
     <t>ぐらい</t>
   </si>
   <si>
@@ -540,9 +522,6 @@
     <t>或者</t>
   </si>
   <si>
-    <t>“あるいは”-&gt;或者；有时</t>
-  </si>
-  <si>
     <t>ないといけない</t>
   </si>
   <si>
@@ -645,9 +624,6 @@
     <t>自谦</t>
   </si>
   <si>
-    <t>ご/お～です-&gt;尊他</t>
-  </si>
-  <si>
     <t>持ち運び</t>
   </si>
   <si>
@@ -775,9 +751,6 @@
   </si>
   <si>
     <t>还…</t>
-  </si>
-  <si>
-    <t>だだ-&gt;只不过</t>
   </si>
   <si>
     <t>辺り</t>
@@ -876,6 +849,74 @@
   </si>
   <si>
     <t>Fre</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>もてあます</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>无法处理；难以应付</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>"つける"-&gt;附着;添加"かける"-&gt;花费</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>かける</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>かかる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>花费；开始；发生；悬挂</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动词</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>他动词</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>けが</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>花费；主动向对方发起的动作</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>“あるいは”-&gt;或者；有时</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>あるいは</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>或者；有时</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ご/お～です-&gt;尊他</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ご/お～です</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>尊他</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>だだ-&gt;只不过;免费</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1257,7 +1298,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F121"/>
+  <dimension ref="A1:F123"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -1269,7 +1310,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1396,13 +1437,13 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>275</v>
       </c>
       <c r="C9" t="s">
         <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>276</v>
       </c>
       <c r="F9" t="s">
         <v>7</v>
@@ -1413,10 +1454,10 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" t="s">
         <v>25</v>
-      </c>
-      <c r="D10" t="s">
-        <v>26</v>
       </c>
       <c r="F10" t="s">
         <v>20</v>
@@ -1427,10 +1468,10 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" t="s">
         <v>27</v>
-      </c>
-      <c r="D11" t="s">
-        <v>28</v>
       </c>
       <c r="F11" t="s">
         <v>20</v>
@@ -1441,13 +1482,13 @@
         <v>5</v>
       </c>
       <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" t="s">
         <v>29</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>30</v>
-      </c>
-      <c r="D12" t="s">
-        <v>31</v>
       </c>
       <c r="F12" t="s">
         <v>7</v>
@@ -1458,10 +1499,10 @@
         <v>5</v>
       </c>
       <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" t="s">
         <v>32</v>
-      </c>
-      <c r="D13" t="s">
-        <v>33</v>
       </c>
       <c r="F13" t="s">
         <v>7</v>
@@ -1472,13 +1513,13 @@
         <v>4</v>
       </c>
       <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" t="s">
         <v>34</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>35</v>
-      </c>
-      <c r="D14" t="s">
-        <v>36</v>
       </c>
       <c r="F14" t="s">
         <v>7</v>
@@ -1489,10 +1530,10 @@
         <v>5</v>
       </c>
       <c r="B15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" t="s">
         <v>37</v>
-      </c>
-      <c r="D15" t="s">
-        <v>38</v>
       </c>
       <c r="F15" t="s">
         <v>20</v>
@@ -1503,10 +1544,10 @@
         <v>5</v>
       </c>
       <c r="B16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" t="s">
         <v>39</v>
-      </c>
-      <c r="D16" t="s">
-        <v>40</v>
       </c>
       <c r="F16" t="s">
         <v>20</v>
@@ -1514,33 +1555,30 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B17" t="s">
-        <v>41</v>
+        <v>279</v>
       </c>
       <c r="D17" t="s">
-        <v>42</v>
+        <v>280</v>
       </c>
       <c r="E17" t="s">
-        <v>43</v>
-      </c>
-      <c r="F17" t="s">
-        <v>7</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>278</v>
       </c>
       <c r="D18" t="s">
-        <v>45</v>
-      </c>
-      <c r="F18" t="s">
-        <v>7</v>
+        <v>284</v>
+      </c>
+      <c r="E18" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.15">
@@ -1548,10 +1586,13 @@
         <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D19" t="s">
-        <v>47</v>
+        <v>41</v>
+      </c>
+      <c r="E19" t="s">
+        <v>277</v>
       </c>
       <c r="F19" t="s">
         <v>7</v>
@@ -1559,33 +1600,33 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A20">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
-      </c>
-      <c r="C20" t="s">
-        <v>49</v>
+        <v>283</v>
       </c>
       <c r="D20" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="F20" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A21">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>51</v>
+        <v>43</v>
+      </c>
+      <c r="C21" t="s">
+        <v>44</v>
       </c>
       <c r="D21" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="F21" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.15">
@@ -1593,10 +1634,10 @@
         <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D22" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="F22" t="s">
         <v>7</v>
@@ -1607,16 +1648,10 @@
         <v>4</v>
       </c>
       <c r="B23" t="s">
-        <v>55</v>
-      </c>
-      <c r="C23" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D23" t="s">
-        <v>57</v>
-      </c>
-      <c r="E23" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="F23" t="s">
         <v>7</v>
@@ -1627,13 +1662,16 @@
         <v>4</v>
       </c>
       <c r="B24" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C24" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D24" t="s">
-        <v>61</v>
+        <v>52</v>
+      </c>
+      <c r="E24" t="s">
+        <v>53</v>
       </c>
       <c r="F24" t="s">
         <v>7</v>
@@ -1641,16 +1679,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B25" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C25" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D25" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="F25" t="s">
         <v>7</v>
@@ -1661,10 +1699,13 @@
         <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>64</v>
+        <v>57</v>
+      </c>
+      <c r="C26" t="s">
+        <v>57</v>
       </c>
       <c r="D26" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="F26" t="s">
         <v>7</v>
@@ -1672,64 +1713,61 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B27" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D27" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="F27" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A28">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B28" t="s">
-        <v>68</v>
-      </c>
-      <c r="C28" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D28" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="F28" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B29" t="s">
-        <v>70</v>
+        <v>63</v>
+      </c>
+      <c r="C29" t="s">
+        <v>63</v>
       </c>
       <c r="D29" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="F29" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B30" t="s">
-        <v>72</v>
-      </c>
-      <c r="C30" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D30" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="F30" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.15">
@@ -1737,10 +1775,13 @@
         <v>3</v>
       </c>
       <c r="B31" t="s">
-        <v>74</v>
+        <v>67</v>
+      </c>
+      <c r="C31" t="s">
+        <v>67</v>
       </c>
       <c r="D31" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="F31" t="s">
         <v>7</v>
@@ -1751,13 +1792,10 @@
         <v>3</v>
       </c>
       <c r="B32" t="s">
-        <v>76</v>
-      </c>
-      <c r="C32" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D32" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F32" t="s">
         <v>7</v>
@@ -1768,13 +1806,13 @@
         <v>3</v>
       </c>
       <c r="B33" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D33" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="F33" t="s">
         <v>7</v>
@@ -1785,10 +1823,13 @@
         <v>3</v>
       </c>
       <c r="B34" t="s">
-        <v>81</v>
+        <v>74</v>
+      </c>
+      <c r="C34" t="s">
+        <v>74</v>
       </c>
       <c r="D34" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="F34" t="s">
         <v>7</v>
@@ -1799,10 +1840,10 @@
         <v>3</v>
       </c>
       <c r="B35" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="D35" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="F35" t="s">
         <v>7</v>
@@ -1810,33 +1851,33 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>85</v>
-      </c>
-      <c r="C36" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D36" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="F36" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B37" t="s">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="C37" t="s">
+        <v>81</v>
       </c>
       <c r="D37" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F37" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.15">
@@ -1844,10 +1885,10 @@
         <v>3</v>
       </c>
       <c r="B38" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="D38" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="F38" t="s">
         <v>7</v>
@@ -1858,10 +1899,10 @@
         <v>3</v>
       </c>
       <c r="B39" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D39" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="F39" t="s">
         <v>7</v>
@@ -1872,13 +1913,10 @@
         <v>3</v>
       </c>
       <c r="B40" t="s">
-        <v>93</v>
-      </c>
-      <c r="C40" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D40" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="F40" t="s">
         <v>7</v>
@@ -1886,13 +1924,16 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B41" t="s">
-        <v>96</v>
+        <v>88</v>
+      </c>
+      <c r="C41" t="s">
+        <v>89</v>
       </c>
       <c r="D41" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="F41" t="s">
         <v>7</v>
@@ -1903,10 +1944,10 @@
         <v>2</v>
       </c>
       <c r="B42" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D42" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="F42" t="s">
         <v>7</v>
@@ -1917,10 +1958,10 @@
         <v>2</v>
       </c>
       <c r="B43" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D43" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="F43" t="s">
         <v>7</v>
@@ -1931,13 +1972,10 @@
         <v>2</v>
       </c>
       <c r="B44" t="s">
-        <v>102</v>
-      </c>
-      <c r="C44" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D44" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="F44" t="s">
         <v>7</v>
@@ -1948,13 +1986,13 @@
         <v>2</v>
       </c>
       <c r="B45" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C45" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="D45" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="F45" t="s">
         <v>7</v>
@@ -1965,13 +2003,13 @@
         <v>2</v>
       </c>
       <c r="B46" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C46" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="D46" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="F46" t="s">
         <v>7</v>
@@ -1982,10 +2020,13 @@
         <v>2</v>
       </c>
       <c r="B47" t="s">
-        <v>111</v>
+        <v>103</v>
+      </c>
+      <c r="C47" t="s">
+        <v>104</v>
       </c>
       <c r="D47" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="F47" t="s">
         <v>7</v>
@@ -1996,10 +2037,10 @@
         <v>2</v>
       </c>
       <c r="B48" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D48" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="F48" t="s">
         <v>7</v>
@@ -2010,10 +2051,10 @@
         <v>2</v>
       </c>
       <c r="B49" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D49" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="F49" t="s">
         <v>7</v>
@@ -2024,10 +2065,10 @@
         <v>2</v>
       </c>
       <c r="B50" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="D50" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="F50" t="s">
         <v>7</v>
@@ -2038,10 +2079,10 @@
         <v>2</v>
       </c>
       <c r="B51" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D51" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="F51" t="s">
         <v>7</v>
@@ -2052,10 +2093,10 @@
         <v>2</v>
       </c>
       <c r="B52" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="D52" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="F52" t="s">
         <v>7</v>
@@ -2066,10 +2107,10 @@
         <v>2</v>
       </c>
       <c r="B53" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D53" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F53" t="s">
         <v>7</v>
@@ -2080,10 +2121,10 @@
         <v>2</v>
       </c>
       <c r="B54" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D54" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="F54" t="s">
         <v>7</v>
@@ -2094,10 +2135,10 @@
         <v>2</v>
       </c>
       <c r="B55" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D55" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F55" t="s">
         <v>7</v>
@@ -2108,10 +2149,10 @@
         <v>2</v>
       </c>
       <c r="B56" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D56" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="F56" t="s">
         <v>7</v>
@@ -2122,10 +2163,10 @@
         <v>2</v>
       </c>
       <c r="B57" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="D57" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="F57" t="s">
         <v>7</v>
@@ -2136,10 +2177,10 @@
         <v>2</v>
       </c>
       <c r="B58" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="D58" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="F58" t="s">
         <v>7</v>
@@ -2150,10 +2191,10 @@
         <v>2</v>
       </c>
       <c r="B59" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="D59" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="F59" t="s">
         <v>7</v>
@@ -2164,10 +2205,10 @@
         <v>2</v>
       </c>
       <c r="B60" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="D60" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="F60" t="s">
         <v>7</v>
@@ -2178,10 +2219,10 @@
         <v>2</v>
       </c>
       <c r="B61" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="D61" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="F61" t="s">
         <v>7</v>
@@ -2192,10 +2233,10 @@
         <v>2</v>
       </c>
       <c r="B62" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="D62" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="F62" t="s">
         <v>7</v>
@@ -2206,13 +2247,10 @@
         <v>2</v>
       </c>
       <c r="B63" t="s">
-        <v>143</v>
-      </c>
-      <c r="C63" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="D63" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="F63" t="s">
         <v>7</v>
@@ -2223,10 +2261,13 @@
         <v>2</v>
       </c>
       <c r="B64" t="s">
-        <v>146</v>
+        <v>138</v>
+      </c>
+      <c r="C64" t="s">
+        <v>139</v>
       </c>
       <c r="D64" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="F64" t="s">
         <v>7</v>
@@ -2237,10 +2278,10 @@
         <v>2</v>
       </c>
       <c r="B65" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D65" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="F65" t="s">
         <v>7</v>
@@ -2248,33 +2289,30 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B66" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="D66" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="F66" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B67" t="s">
-        <v>152</v>
-      </c>
-      <c r="C67" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="D67" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="F67" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.15">
@@ -2282,13 +2320,13 @@
         <v>2</v>
       </c>
       <c r="B68" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C68" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="D68" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="F68" t="s">
         <v>7</v>
@@ -2296,19 +2334,19 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B69" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="C69" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="D69" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F69" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.15">
@@ -2316,13 +2354,13 @@
         <v>3</v>
       </c>
       <c r="B70" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C70" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="D70" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="F70" t="s">
         <v>20</v>
@@ -2330,16 +2368,19 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B71" t="s">
-        <v>161</v>
+        <v>156</v>
+      </c>
+      <c r="C71" t="s">
+        <v>157</v>
       </c>
       <c r="D71" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="F71" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.15">
@@ -2347,10 +2388,10 @@
         <v>2</v>
       </c>
       <c r="B72" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="D72" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="F72" t="s">
         <v>7</v>
@@ -2361,13 +2402,13 @@
         <v>2</v>
       </c>
       <c r="B73" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="C73" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="D73" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="F73" t="s">
         <v>7</v>
@@ -2378,47 +2419,41 @@
         <v>2</v>
       </c>
       <c r="B74" t="s">
-        <v>170</v>
+        <v>286</v>
       </c>
       <c r="D74" t="s">
-        <v>171</v>
-      </c>
-      <c r="E74" t="s">
-        <v>172</v>
-      </c>
-      <c r="F74" t="s">
-        <v>7</v>
+        <v>287</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B75" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="D75" t="s">
-        <v>174</v>
+        <v>165</v>
+      </c>
+      <c r="E75" t="s">
+        <v>285</v>
       </c>
       <c r="F75" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B76" t="s">
-        <v>175</v>
-      </c>
-      <c r="C76" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="D76" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="F76" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.15">
@@ -2426,10 +2461,13 @@
         <v>2</v>
       </c>
       <c r="B77" t="s">
-        <v>178</v>
+        <v>168</v>
+      </c>
+      <c r="C77" t="s">
+        <v>169</v>
       </c>
       <c r="D77" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="F77" t="s">
         <v>7</v>
@@ -2440,10 +2478,10 @@
         <v>2</v>
       </c>
       <c r="B78" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="D78" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="F78" t="s">
         <v>7</v>
@@ -2454,10 +2492,10 @@
         <v>2</v>
       </c>
       <c r="B79" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="D79" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F79" t="s">
         <v>7</v>
@@ -2468,10 +2506,10 @@
         <v>2</v>
       </c>
       <c r="B80" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="D80" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="F80" t="s">
         <v>7</v>
@@ -2482,10 +2520,10 @@
         <v>2</v>
       </c>
       <c r="B81" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="D81" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="F81" t="s">
         <v>7</v>
@@ -2496,10 +2534,10 @@
         <v>2</v>
       </c>
       <c r="B82" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="D82" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="F82" t="s">
         <v>7</v>
@@ -2510,10 +2548,10 @@
         <v>2</v>
       </c>
       <c r="B83" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="D83" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="F83" t="s">
         <v>7</v>
@@ -2524,10 +2562,10 @@
         <v>2</v>
       </c>
       <c r="B84" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="D84" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="F84" t="s">
         <v>7</v>
@@ -2538,10 +2576,10 @@
         <v>2</v>
       </c>
       <c r="B85" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="D85" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="F85" t="s">
         <v>7</v>
@@ -2549,16 +2587,13 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B86" t="s">
-        <v>196</v>
-      </c>
-      <c r="C86" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="D86" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="F86" t="s">
         <v>7</v>
@@ -2569,13 +2604,13 @@
         <v>1</v>
       </c>
       <c r="B87" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="C87" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="D87" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="F87" t="s">
         <v>7</v>
@@ -2586,13 +2621,13 @@
         <v>1</v>
       </c>
       <c r="B88" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="C88" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="D88" t="s">
-        <v>99</v>
+        <v>193</v>
       </c>
       <c r="F88" t="s">
         <v>7</v>
@@ -2603,13 +2638,13 @@
         <v>1</v>
       </c>
       <c r="B89" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="C89" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="D89" t="s">
-        <v>204</v>
+        <v>94</v>
       </c>
       <c r="F89" t="s">
         <v>7</v>
@@ -2620,13 +2655,13 @@
         <v>1</v>
       </c>
       <c r="B90" t="s">
-        <v>205</v>
+        <v>196</v>
+      </c>
+      <c r="C90" t="s">
+        <v>196</v>
       </c>
       <c r="D90" t="s">
-        <v>206</v>
-      </c>
-      <c r="E90" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="F90" t="s">
         <v>7</v>
@@ -2637,16 +2672,10 @@
         <v>1</v>
       </c>
       <c r="B91" t="s">
-        <v>208</v>
-      </c>
-      <c r="C91" t="s">
-        <v>209</v>
+        <v>289</v>
       </c>
       <c r="D91" t="s">
-        <v>210</v>
-      </c>
-      <c r="F91" t="s">
-        <v>7</v>
+        <v>290</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.15">
@@ -2654,13 +2683,13 @@
         <v>1</v>
       </c>
       <c r="B92" t="s">
-        <v>211</v>
-      </c>
-      <c r="C92" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="D92" t="s">
-        <v>213</v>
+        <v>199</v>
+      </c>
+      <c r="E92" t="s">
+        <v>288</v>
       </c>
       <c r="F92" t="s">
         <v>7</v>
@@ -2671,13 +2700,13 @@
         <v>1</v>
       </c>
       <c r="B93" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="C93" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="D93" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="F93" t="s">
         <v>7</v>
@@ -2685,16 +2714,16 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B94" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="C94" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="D94" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="F94" t="s">
         <v>7</v>
@@ -2705,16 +2734,16 @@
         <v>1</v>
       </c>
       <c r="B95" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="C95" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="D95" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="F95" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.15">
@@ -2722,13 +2751,13 @@
         <v>0</v>
       </c>
       <c r="B96" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="C96" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="D96" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="F96" t="s">
         <v>7</v>
@@ -2736,19 +2765,19 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A97">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B97" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="C97" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="D97" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="F97" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.15">
@@ -2756,13 +2785,13 @@
         <v>0</v>
       </c>
       <c r="B98" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="C98" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="D98" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F98" t="s">
         <v>7</v>
@@ -2773,13 +2802,13 @@
         <v>0</v>
       </c>
       <c r="B99" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="C99" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="D99" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="F99" t="s">
         <v>7</v>
@@ -2790,13 +2819,13 @@
         <v>0</v>
       </c>
       <c r="B100" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="C100" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="D100" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="F100" t="s">
         <v>7</v>
@@ -2807,16 +2836,13 @@
         <v>0</v>
       </c>
       <c r="B101" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="C101" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="D101" t="s">
-        <v>233</v>
-      </c>
-      <c r="E101" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="F101" t="s">
         <v>7</v>
@@ -2827,13 +2853,13 @@
         <v>0</v>
       </c>
       <c r="B102" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="C102" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="D102" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="F102" t="s">
         <v>7</v>
@@ -2844,13 +2870,16 @@
         <v>0</v>
       </c>
       <c r="B103" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="C103" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="D103" t="s">
-        <v>239</v>
+        <v>225</v>
+      </c>
+      <c r="E103" t="s">
+        <v>226</v>
       </c>
       <c r="F103" t="s">
         <v>7</v>
@@ -2861,13 +2890,13 @@
         <v>0</v>
       </c>
       <c r="B104" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="C104" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D104" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="F104" t="s">
         <v>7</v>
@@ -2878,13 +2907,13 @@
         <v>0</v>
       </c>
       <c r="B105" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="C105" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="D105" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="F105" t="s">
         <v>7</v>
@@ -2895,13 +2924,13 @@
         <v>0</v>
       </c>
       <c r="B106" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="C106" t="s">
-        <v>245</v>
+        <v>217</v>
       </c>
       <c r="D106" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="F106" t="s">
         <v>7</v>
@@ -2912,10 +2941,13 @@
         <v>0</v>
       </c>
       <c r="B107" t="s">
-        <v>247</v>
+        <v>234</v>
+      </c>
+      <c r="C107" t="s">
+        <v>234</v>
       </c>
       <c r="D107" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="F107" t="s">
         <v>7</v>
@@ -2926,13 +2958,13 @@
         <v>0</v>
       </c>
       <c r="B108" t="s">
-        <v>249</v>
+        <v>236</v>
+      </c>
+      <c r="C108" t="s">
+        <v>237</v>
       </c>
       <c r="D108" t="s">
-        <v>250</v>
-      </c>
-      <c r="E108" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="F108" t="s">
         <v>7</v>
@@ -2943,13 +2975,10 @@
         <v>0</v>
       </c>
       <c r="B109" t="s">
-        <v>252</v>
-      </c>
-      <c r="C109" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D109" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="F109" t="s">
         <v>7</v>
@@ -2960,10 +2989,13 @@
         <v>0</v>
       </c>
       <c r="B110" t="s">
-        <v>170</v>
+        <v>241</v>
       </c>
       <c r="D110" t="s">
-        <v>255</v>
+        <v>242</v>
+      </c>
+      <c r="E110" t="s">
+        <v>291</v>
       </c>
       <c r="F110" t="s">
         <v>7</v>
@@ -2974,13 +3006,13 @@
         <v>0</v>
       </c>
       <c r="B111" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="C111" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="D111" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="F111" t="s">
         <v>7</v>
@@ -2991,10 +3023,10 @@
         <v>0</v>
       </c>
       <c r="B112" t="s">
-        <v>259</v>
+        <v>164</v>
       </c>
       <c r="D112" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="F112" t="s">
         <v>7</v>
@@ -3005,13 +3037,13 @@
         <v>0</v>
       </c>
       <c r="B113" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="C113" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="D113" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="F113" t="s">
         <v>7</v>
@@ -3022,13 +3054,10 @@
         <v>0</v>
       </c>
       <c r="B114" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="D114" t="s">
-        <v>264</v>
-      </c>
-      <c r="E114" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="F114" t="s">
         <v>7</v>
@@ -3039,13 +3068,13 @@
         <v>0</v>
       </c>
       <c r="B115" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="C115" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="D115" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="F115" t="s">
         <v>7</v>
@@ -3056,13 +3085,13 @@
         <v>0</v>
       </c>
       <c r="B116" t="s">
-        <v>268</v>
-      </c>
-      <c r="C116" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="D116" t="s">
-        <v>269</v>
+        <v>255</v>
+      </c>
+      <c r="E116" t="s">
+        <v>256</v>
       </c>
       <c r="F116" t="s">
         <v>7</v>
@@ -3073,13 +3102,13 @@
         <v>0</v>
       </c>
       <c r="B117" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="C117" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="D117" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="F117" t="s">
         <v>7</v>
@@ -3090,13 +3119,13 @@
         <v>0</v>
       </c>
       <c r="B118" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="F118" t="s">
         <v>7</v>
@@ -3104,16 +3133,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A119">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B119" t="s">
-        <v>276</v>
+        <v>261</v>
+      </c>
+      <c r="C119" t="s">
+        <v>262</v>
       </c>
       <c r="D119" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="F119" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.15">
@@ -3121,13 +3153,13 @@
         <v>0</v>
       </c>
       <c r="B120" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="C120" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="D120" t="s">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="F120" t="s">
         <v>7</v>
@@ -3138,13 +3170,44 @@
         <v>1</v>
       </c>
       <c r="B121" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="D121" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="F121" t="s">
-        <v>282</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A122">
+        <v>0</v>
+      </c>
+      <c r="B122" t="s">
+        <v>269</v>
+      </c>
+      <c r="C122" t="s">
+        <v>269</v>
+      </c>
+      <c r="D122" t="s">
+        <v>270</v>
+      </c>
+      <c r="F122" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A123">
+        <v>1</v>
+      </c>
+      <c r="B123" t="s">
+        <v>271</v>
+      </c>
+      <c r="D123" t="s">
+        <v>272</v>
+      </c>
+      <c r="F123" t="s">
+        <v>273</v>
       </c>
     </row>
   </sheetData>
